--- a/satisfaction_surveys/006_nail_polish_durability_expectation_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/006_nail_polish_durability_expectation_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1_month'}</t>
+          <t>less_than_1_month</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1 month'}</t>
+          <t>Less than 1 month</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_1_month'}</t>
+          <t>more_than_1_month</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'More than 1 month'}</t>
+          <t>More than 1 month</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_3_months'}</t>
+          <t>more_than_3_months</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'More than 3 months'}</t>
+          <t>More than 3 months</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_6_months'}</t>
+          <t>more_than_6_months</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'More than 6 months'}</t>
+          <t>More than 6 months</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'opi'}</t>
+          <t>opi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'OPI'}</t>
+          <t>OPI</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'essie'}</t>
+          <t>essie</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Essie'}</t>
+          <t>Essie</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'revlon'}</t>
+          <t>revlon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Revlon'}</t>
+          <t>Revlon</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'sally_hansen'}</t>
+          <t>sally_hansen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Sally Hansen'}</t>
+          <t>Sally Hansen</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'nail_lacquer'}</t>
+          <t>nail_lacquer</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Nail Lacquer'}</t>
+          <t>Nail Lacquer</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'nail_enamel'}</t>
+          <t>nail_enamel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Nail Enamel'}</t>
+          <t>Nail Enamel</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
